--- a/output/2026-09-07/enriched_analysis.xlsx
+++ b/output/2026-09-07/enriched_analysis.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BB49"/>
+  <dimension ref="A1:BB50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -766,7 +766,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="Q2" t="n">
-        <v>2593</v>
+        <v>2566</v>
       </c>
       <c r="R2" t="n">
-        <v>8.91</v>
+        <v>8.83</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.411</v>
+        <v>0.412</v>
       </c>
       <c r="Q3" t="n">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="R3" t="n">
         <v>27.4</v>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.042</v>
+        <v>0.043</v>
       </c>
       <c r="Q4" t="n">
-        <v>17016</v>
+        <v>16882</v>
       </c>
       <c r="R4" t="n">
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="S4" t="n">
         <v>83</v>
@@ -1307,12 +1307,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONFIPET</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONFIDENCE PETROLEUM INDIA LIMITED</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -1336,22 +1336,22 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>82.18000000000001</v>
+        <v>319.85</v>
       </c>
       <c r="J5" t="n">
-        <v>72.78</v>
+        <v>217.8</v>
       </c>
       <c r="K5" t="n">
-        <v>12.9</v>
+        <v>46.9</v>
       </c>
       <c r="L5" t="n">
-        <v>61.32</v>
+        <v>71.75</v>
       </c>
       <c r="M5" t="n">
-        <v>82.39</v>
+        <v>0.82</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1359,83 +1359,83 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.016</v>
+        <v>0.056</v>
       </c>
       <c r="Q5" t="n">
-        <v>2732</v>
+        <v>1458</v>
       </c>
       <c r="R5" t="n">
-        <v>21.4</v>
+        <v>19.6</v>
       </c>
       <c r="S5" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="T5" t="n">
-        <v>136</v>
+        <v>40</v>
       </c>
       <c r="U5" t="n">
         <v>54</v>
       </c>
       <c r="V5" t="n">
-        <v>1.83</v>
+        <v>8.23</v>
       </c>
       <c r="W5" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="X5" t="n">
-        <v>0.4</v>
+        <v>0.01</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>221.01</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>183.27</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>215.9638691452524</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>20-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>26-08-2026</t>
+        </is>
+      </c>
+      <c r="AK5" t="n">
         <v>6</v>
       </c>
-      <c r="AA5" t="n">
-        <v>76.87</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>53.23</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>172.1</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>72.54271810256775</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Mature — Wait for Pullback</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>19-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>26-08-2026</t>
-        </is>
-      </c>
-      <c r="AK5" t="n">
-        <v>68</v>
-      </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="AM5" t="n">
         <v>12</v>
@@ -1444,40 +1444,40 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>90512030</v>
+        <v>5939298</v>
       </c>
       <c r="AU5" t="n">
-        <v>495980620</v>
+        <v>9479950</v>
       </c>
       <c r="AV5" t="n">
-        <v>495980620</v>
+        <v>9479950</v>
       </c>
       <c r="AW5" t="n">
-        <v>1205171980</v>
+        <v>9479950</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>495980620</v>
+        <v>9479950</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -1489,12 +1489,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>CONFIPET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>CONFIDENCE PETROLEUM INDIA LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -1518,22 +1518,22 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>319.85</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>217.8</v>
+        <v>72.78</v>
       </c>
       <c r="K6" t="n">
-        <v>46.9</v>
+        <v>12.9</v>
       </c>
       <c r="L6" t="n">
-        <v>71.75</v>
+        <v>61.32</v>
       </c>
       <c r="M6" t="n">
-        <v>0.82</v>
+        <v>82.39</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1541,52 +1541,52 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.058</v>
+        <v>2.957</v>
       </c>
       <c r="Q6" t="n">
-        <v>1403</v>
+        <v>2786</v>
       </c>
       <c r="R6" t="n">
-        <v>18.9</v>
+        <v>21.8</v>
       </c>
       <c r="S6" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="T6" t="n">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="U6" t="n">
         <v>54</v>
       </c>
       <c r="V6" t="n">
-        <v>8.23</v>
+        <v>1.83</v>
       </c>
       <c r="W6" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="X6" t="n">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="Y6" t="b">
         <v>1</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AA6" t="n">
-        <v>221.01</v>
+        <v>76.87</v>
       </c>
       <c r="AB6" t="n">
-        <v>183.27</v>
+        <v>53.23</v>
       </c>
       <c r="AC6" t="n">
-        <v>113.7</v>
+        <v>172.1</v>
       </c>
       <c r="AD6" t="n">
-        <v>215.9638691452524</v>
+        <v>72.54271810256775</v>
       </c>
       <c r="AE6" t="n">
-        <v>48.1</v>
+        <v>13.3</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>19-06-2026</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1614,10 +1614,10 @@
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="AL6" t="n">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
         <v>12</v>
@@ -1626,40 +1626,40 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AR6" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>5939298</v>
+        <v>90512030</v>
       </c>
       <c r="AU6" t="n">
-        <v>9479950</v>
+        <v>495980620</v>
       </c>
       <c r="AV6" t="n">
-        <v>9479950</v>
+        <v>495980620</v>
       </c>
       <c r="AW6" t="n">
-        <v>9479950</v>
+        <v>1205171980</v>
       </c>
       <c r="AX6" t="n">
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>9479950</v>
+        <v>495980620</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
       <c r="Q7" t="n">
-        <v>15724</v>
+        <v>15863</v>
       </c>
       <c r="R7" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="S7" t="n">
         <v>16</v>
@@ -1853,12 +1853,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1870,157 +1870,155 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>66.91</v>
+        <v>202.13</v>
       </c>
       <c r="J8" t="n">
-        <v>70.34999999999999</v>
+        <v>164.1</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.9</v>
+        <v>23.2</v>
       </c>
       <c r="L8" t="n">
-        <v>72.56999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>0.25</v>
       </c>
       <c r="N8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.533</v>
+        <v>0.006</v>
       </c>
       <c r="Q8" t="n">
-        <v>195</v>
-      </c>
-      <c r="R8" t="n">
-        <v>8.300000000000001</v>
-      </c>
+        <v>4321</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="T8" t="n">
-        <v>27.97</v>
+        <v>258</v>
       </c>
       <c r="U8" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="V8" t="n">
-        <v>2.73</v>
+        <v>-1.13</v>
       </c>
       <c r="W8" t="n">
-        <v>13.7</v>
+        <v>6.38</v>
       </c>
       <c r="X8" t="n">
-        <v>1.86</v>
+        <v>10.11</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.140000000000001</v>
+        <v>61</v>
       </c>
       <c r="AA8" t="n">
-        <v>58.12</v>
+        <v>180.03</v>
       </c>
       <c r="AB8" t="n">
-        <v>51.72</v>
+        <v>178.21</v>
       </c>
       <c r="AC8" t="n">
-        <v>47.7</v>
+        <v>22.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>70.34939033874578</v>
+        <v>164.1047741935484</v>
       </c>
       <c r="AE8" t="n">
-        <v>-4.9</v>
+        <v>23.2</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="AM8" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="AN8" t="n">
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AR8" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>3378057</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>10402494</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>10402494</v>
+        <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>10402494</v>
+        <v>1664671</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>10402494</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
         <v>1</v>
@@ -2035,12 +2033,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2052,155 +2050,157 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F9" t="n">
         <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>202.13</v>
+        <v>66.91</v>
       </c>
       <c r="J9" t="n">
-        <v>164.1</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>23.2</v>
+        <v>-4.9</v>
       </c>
       <c r="L9" t="n">
-        <v>60.6</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.25</v>
+        <v>1.04</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.006</v>
+        <v>0.507</v>
       </c>
       <c r="Q9" t="n">
-        <v>4285</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8.720000000000001</v>
+      </c>
       <c r="S9" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="T9" t="n">
-        <v>258</v>
+        <v>27.97</v>
       </c>
       <c r="U9" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.13</v>
+        <v>2.73</v>
       </c>
       <c r="W9" t="n">
-        <v>6.38</v>
+        <v>13.7</v>
       </c>
       <c r="X9" t="n">
-        <v>10.11</v>
+        <v>1.86</v>
       </c>
       <c r="Y9" t="b">
         <v>1</v>
       </c>
       <c r="Z9" t="n">
-        <v>61</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>180.03</v>
+        <v>58.12</v>
       </c>
       <c r="AB9" t="n">
-        <v>178.21</v>
+        <v>51.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>22.3</v>
+        <v>47.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>164.1047741935484</v>
+        <v>70.34939033874578</v>
       </c>
       <c r="AE9" t="n">
-        <v>23.2</v>
+        <v>-4.9</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>09-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AL9" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>3378057</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>10402494</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>10402494</v>
       </c>
       <c r="AW9" t="n">
-        <v>1664671</v>
+        <v>10402494</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>10402494</v>
       </c>
       <c r="AZ9" t="n">
         <v>1</v>
@@ -2215,108 +2215,108 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Strong Buy Setup</t>
+          <t>Buy on Breakout</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F10" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>267.15</v>
+        <v>108.05</v>
       </c>
       <c r="J10" t="n">
-        <v>243.52</v>
+        <v>91.7</v>
       </c>
       <c r="K10" t="n">
-        <v>9.699999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="L10" t="n">
-        <v>67.65000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="M10" t="n">
-        <v>1.11</v>
+        <v>8.49</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.16</v>
+        <v>0.298</v>
       </c>
       <c r="Q10" t="n">
-        <v>693</v>
+        <v>2850</v>
       </c>
       <c r="R10" t="n">
-        <v>57.9</v>
+        <v>23.4</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T10" t="n">
-        <v>2.99</v>
+        <v>14</v>
       </c>
       <c r="U10" t="n">
-        <v>97</v>
+        <v>-14</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="W10" t="n">
-        <v>11.6</v>
+        <v>16.9</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>16.21</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
-        <v>250.74</v>
+        <v>91.86</v>
       </c>
       <c r="AB10" t="n">
-        <v>181.35</v>
+        <v>92.13</v>
       </c>
       <c r="AC10" t="n">
-        <v>87.40000000000001</v>
+        <v>25.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>238.0921052631579</v>
+        <v>91.7739742726077</v>
       </c>
       <c r="AE10" t="n">
-        <v>12.2</v>
+        <v>17.7</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -2331,78 +2331,78 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="AM10" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>23357076</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>35618957</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>85826103</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>85826103</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>85826103</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>23357076</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>85826103</v>
+      </c>
+      <c r="AZ10" t="n">
         <v>1</v>
       </c>
-      <c r="AP10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>4065000</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4065000</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>18095000</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>18095000</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>4065000</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>2</v>
-      </c>
       <c r="BA10" t="n">
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>0.2721</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G11" t="n">
         <v>25</v>
@@ -2426,84 +2426,84 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>108.05</v>
+        <v>391.15</v>
       </c>
       <c r="J11" t="n">
-        <v>91.7</v>
+        <v>338.1</v>
       </c>
       <c r="K11" t="n">
-        <v>17.8</v>
+        <v>15.7</v>
       </c>
       <c r="L11" t="n">
-        <v>70.88</v>
+        <v>66.73</v>
       </c>
       <c r="M11" t="n">
-        <v>8.49</v>
+        <v>0.34</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.306</v>
+        <v>0.073</v>
       </c>
       <c r="Q11" t="n">
-        <v>2775</v>
+        <v>464</v>
       </c>
       <c r="R11" t="n">
-        <v>22.7</v>
+        <v>13.7</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="T11" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="U11" t="n">
-        <v>-14</v>
+        <v>33</v>
       </c>
       <c r="V11" t="n">
-        <v>0.57</v>
+        <v>14.36</v>
       </c>
       <c r="W11" t="n">
-        <v>16.9</v>
+        <v>9.94</v>
       </c>
       <c r="X11" t="n">
-        <v>0.01</v>
+        <v>0.23</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AA11" t="n">
-        <v>91.86</v>
+        <v>330.91</v>
       </c>
       <c r="AB11" t="n">
-        <v>92.13</v>
+        <v>262.37</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.2</v>
+        <v>79.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>91.7739742726077</v>
+        <v>338.1</v>
       </c>
       <c r="AE11" t="n">
-        <v>17.7</v>
+        <v>15.7</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -2513,58 +2513,58 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS11" t="n">
-        <v>23357076</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>35618957</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>85826103</v>
+        <v>3381000</v>
       </c>
       <c r="AV11" t="n">
-        <v>85826103</v>
+        <v>3381000</v>
       </c>
       <c r="AW11" t="n">
-        <v>85826103</v>
+        <v>3381000</v>
       </c>
       <c r="AX11" t="n">
-        <v>23357076</v>
+        <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>85826103</v>
+        <v>3381000</v>
       </c>
       <c r="AZ11" t="n">
         <v>1</v>
@@ -2573,18 +2573,18 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.2721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -2596,87 +2596,87 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="I12" t="n">
-        <v>391.15</v>
+        <v>267.15</v>
       </c>
       <c r="J12" t="n">
-        <v>338.1</v>
+        <v>243.52</v>
       </c>
       <c r="K12" t="n">
-        <v>15.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>66.73</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>0.34</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>25-08-2026</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>726</v>
+      </c>
+      <c r="R12" t="n">
+        <v>60.7</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U12" t="n">
+        <v>97</v>
+      </c>
+      <c r="V12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>11-08-2026</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>461</v>
-      </c>
-      <c r="R12" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-8</v>
-      </c>
-      <c r="T12" t="n">
-        <v>24</v>
-      </c>
-      <c r="U12" t="n">
-        <v>33</v>
-      </c>
-      <c r="V12" t="n">
-        <v>14.36</v>
-      </c>
       <c r="W12" t="n">
-        <v>9.94</v>
+        <v>11.6</v>
       </c>
       <c r="X12" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>18</v>
+        <v>16.21</v>
       </c>
       <c r="AA12" t="n">
-        <v>330.91</v>
+        <v>250.74</v>
       </c>
       <c r="AB12" t="n">
-        <v>262.37</v>
+        <v>181.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>79.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>338.1</v>
+        <v>238.0921052631579</v>
       </c>
       <c r="AE12" t="n">
-        <v>15.7</v>
+        <v>12.2</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2695,61 +2695,61 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
         <v>1</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>4065000</v>
       </c>
       <c r="AU12" t="n">
-        <v>3381000</v>
+        <v>4065000</v>
       </c>
       <c r="AV12" t="n">
-        <v>3381000</v>
+        <v>18095000</v>
       </c>
       <c r="AW12" t="n">
-        <v>3381000</v>
+        <v>18095000</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>3381000</v>
+        <v>4065000</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0.007</v>
       </c>
       <c r="Q13" t="n">
-        <v>5991</v>
+        <v>5932</v>
       </c>
       <c r="R13" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S13" t="n">
         <v>43</v>
@@ -2995,13 +2995,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.744</v>
+        <v>0.841</v>
       </c>
       <c r="Q14" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="R14" t="n">
-        <v>87.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="S14" t="n">
         <v>-1</v>
@@ -3019,7 +3019,7 @@
         <v>-0.18</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y14" t="b">
         <v>0</v>
@@ -3177,13 +3177,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.616</v>
+        <v>0.61</v>
       </c>
       <c r="Q15" t="n">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="R15" t="n">
-        <v>40</v>
+        <v>40.5</v>
       </c>
       <c r="S15" t="n">
         <v>21</v>
@@ -3307,12 +3307,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -3324,87 +3324,87 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I16" t="n">
-        <v>531.6</v>
+        <v>121.75</v>
       </c>
       <c r="J16" t="n">
-        <v>482.22</v>
+        <v>113.51</v>
       </c>
       <c r="K16" t="n">
-        <v>10.2</v>
+        <v>7.3</v>
       </c>
       <c r="L16" t="n">
-        <v>62.09</v>
+        <v>73.48</v>
       </c>
       <c r="M16" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.308</v>
       </c>
       <c r="Q16" t="n">
-        <v>914</v>
+        <v>234</v>
       </c>
       <c r="R16" t="n">
-        <v>8.99</v>
+        <v>27.9</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="T16" t="n">
-        <v>30</v>
+        <v>12.07</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="V16" t="n">
-        <v>14.66</v>
+        <v>1.02</v>
       </c>
       <c r="W16" t="n">
-        <v>14.4</v>
+        <v>7.92</v>
       </c>
       <c r="X16" t="n">
-        <v>0.01</v>
+        <v>0.98</v>
       </c>
       <c r="Y16" t="b">
         <v>1</v>
       </c>
       <c r="Z16" t="n">
-        <v>14</v>
+        <v>4.11</v>
       </c>
       <c r="AA16" t="n">
-        <v>491.46</v>
+        <v>111.36</v>
       </c>
       <c r="AB16" t="n">
-        <v>488.23</v>
+        <v>119.46</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.2</v>
+        <v>12.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>482.2203068647228</v>
+        <v>113.5917789436032</v>
       </c>
       <c r="AE16" t="n">
-        <v>10.2</v>
+        <v>7.2</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -3413,68 +3413,68 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AK16" t="n">
+        <v>87</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>91</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO16" t="n">
         <v>7</v>
       </c>
-      <c r="AL16" t="n">
-        <v>12</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>6</v>
-      </c>
       <c r="AP16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>2234158</v>
+        <v>1640584</v>
       </c>
       <c r="AT16" t="n">
-        <v>7888642</v>
+        <v>3936339</v>
       </c>
       <c r="AU16" t="n">
-        <v>7888642</v>
+        <v>4899099</v>
       </c>
       <c r="AV16" t="n">
-        <v>7888642</v>
+        <v>4899099</v>
       </c>
       <c r="AW16" t="n">
-        <v>7888642</v>
+        <v>6295322</v>
       </c>
       <c r="AX16" t="n">
-        <v>2234158</v>
+        <v>1640584</v>
       </c>
       <c r="AY16" t="n">
-        <v>7888642</v>
+        <v>4899099</v>
       </c>
       <c r="AZ16" t="n">
         <v>1</v>
@@ -3483,18 +3483,18 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.2832</v>
+        <v>0.3349</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3506,153 +3506,157 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F17" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>19.63</v>
+        <v>531.6</v>
       </c>
       <c r="J17" t="n">
-        <v>21.01</v>
+        <v>482.22</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.6</v>
+        <v>10.2</v>
       </c>
       <c r="L17" t="n">
-        <v>70.87</v>
+        <v>62.09</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.135</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>371</v>
+        <v>910</v>
       </c>
       <c r="R17" t="n">
-        <v>5.99</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>118</v>
-      </c>
-      <c r="T17" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>30</v>
+      </c>
       <c r="U17" t="n">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>14.66</v>
       </c>
       <c r="W17" t="n">
-        <v>18.5</v>
+        <v>14.4</v>
       </c>
       <c r="X17" t="n">
         <v>0.01</v>
       </c>
       <c r="Y17" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14</v>
+      </c>
       <c r="AA17" t="n">
-        <v>18.55</v>
+        <v>491.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>15.18</v>
+        <v>488.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>45.2</v>
+        <v>20.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>21.00741139152052</v>
+        <v>482.2203068647228</v>
       </c>
       <c r="AE17" t="n">
-        <v>-6.6</v>
+        <v>10.2</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="AK17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN17" t="n">
         <v>2</v>
       </c>
-      <c r="AL17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>0</v>
-      </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AP17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AR17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2234158</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>7888642</v>
       </c>
       <c r="AU17" t="n">
-        <v>4960333</v>
+        <v>7888642</v>
       </c>
       <c r="AV17" t="n">
-        <v>4960333</v>
+        <v>7888642</v>
       </c>
       <c r="AW17" t="n">
-        <v>4960333</v>
+        <v>7888642</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>2234158</v>
       </c>
       <c r="AY17" t="n">
-        <v>4960333</v>
+        <v>7888642</v>
       </c>
       <c r="AZ17" t="n">
         <v>1</v>
@@ -3661,18 +3665,18 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>0.2832</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -3684,177 +3688,173 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H18" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>184.4</v>
+        <v>19.63</v>
       </c>
       <c r="J18" t="n">
-        <v>170.45</v>
+        <v>21.01</v>
       </c>
       <c r="K18" t="n">
-        <v>8.199999999999999</v>
+        <v>-6.6</v>
       </c>
       <c r="L18" t="n">
-        <v>67.54000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="M18" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>385</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="S18" t="n">
+        <v>118</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>391</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>15.18</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>45.2</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>21.00741139152052</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>-6.6</v>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>19-08-2026</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
         <v>2</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>248</v>
-      </c>
-      <c r="R18" t="n">
-        <v>26.6</v>
-      </c>
-      <c r="S18" t="n">
-        <v>24</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U18" t="n">
-        <v>-31</v>
-      </c>
-      <c r="V18" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="W18" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="b">
+      <c r="AL18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>19</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4960333</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4960333</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4960333</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>4960333</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>1</v>
       </c>
-      <c r="Z18" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>177.14</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>161.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>170.4518641810919</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Early Accumulation</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Early Accumulation</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>03-09-2026</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>5120374</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>5120374</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5120374</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>5120374</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>5120374</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>5120374</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>5120374</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2</v>
-      </c>
       <c r="BA18" t="n">
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -3866,125 +3866,127 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F19" t="n">
         <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I19" t="n">
-        <v>963.15</v>
+        <v>184.4</v>
       </c>
       <c r="J19" t="n">
-        <v>717.77</v>
+        <v>170.45</v>
       </c>
       <c r="K19" t="n">
-        <v>34.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>61.71</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>1.61</v>
+        <v>0.26</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0.54</v>
+        <v>0.101</v>
       </c>
       <c r="Q19" t="n">
-        <v>298</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
+        <v>257</v>
+      </c>
+      <c r="R19" t="n">
+        <v>27.5</v>
+      </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="T19" t="n">
-        <v>11.91</v>
+        <v>1.87</v>
       </c>
       <c r="U19" t="n">
-        <v>-184</v>
+        <v>-31</v>
       </c>
       <c r="V19" t="n">
-        <v>31.98</v>
+        <v>3.36</v>
       </c>
       <c r="W19" t="n">
-        <v>0.27</v>
+        <v>4.96</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>57.93</v>
+        <v>2.97</v>
       </c>
       <c r="AA19" t="n">
-        <v>733.46</v>
+        <v>177.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>763.3</v>
+        <v>161.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>24.6</v>
+        <v>32.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>712.9228174663466</v>
+        <v>170.4518641810919</v>
       </c>
       <c r="AE19" t="n">
-        <v>35.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP19" t="n">
         <v>4</v>
@@ -3996,45 +3998,45 @@
         <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>5120374</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>5120374</v>
       </c>
       <c r="AU19" t="n">
-        <v>23461577</v>
+        <v>5120374</v>
       </c>
       <c r="AV19" t="n">
-        <v>23461577</v>
+        <v>5120374</v>
       </c>
       <c r="AW19" t="n">
-        <v>23461577</v>
+        <v>5120374</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>5120374</v>
       </c>
       <c r="AY19" t="n">
-        <v>23461577</v>
+        <v>5120374</v>
       </c>
       <c r="AZ19" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -4046,91 +4048,89 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F20" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G20" t="n">
         <v>25</v>
       </c>
       <c r="H20" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>121.75</v>
+        <v>963.15</v>
       </c>
       <c r="J20" t="n">
-        <v>113.51</v>
+        <v>717.77</v>
       </c>
       <c r="K20" t="n">
-        <v>7.3</v>
+        <v>34.2</v>
       </c>
       <c r="L20" t="n">
-        <v>73.48</v>
+        <v>61.71</v>
       </c>
       <c r="M20" t="n">
-        <v>0.72</v>
+        <v>1.61</v>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.312</v>
+        <v>0.521</v>
       </c>
       <c r="Q20" t="n">
-        <v>231</v>
-      </c>
-      <c r="R20" t="n">
-        <v>27.4</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="T20" t="n">
-        <v>12.07</v>
+        <v>11.91</v>
       </c>
       <c r="U20" t="n">
-        <v>-29</v>
+        <v>-184</v>
       </c>
       <c r="V20" t="n">
-        <v>1.02</v>
+        <v>31.98</v>
       </c>
       <c r="W20" t="n">
-        <v>7.92</v>
+        <v>0.27</v>
       </c>
       <c r="X20" t="n">
-        <v>0.98</v>
+        <v>0.1</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.11</v>
+        <v>57.93</v>
       </c>
       <c r="AA20" t="n">
-        <v>111.36</v>
+        <v>733.46</v>
       </c>
       <c r="AB20" t="n">
-        <v>119.46</v>
+        <v>763.3</v>
       </c>
       <c r="AC20" t="n">
-        <v>12.8</v>
+        <v>24.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>113.5917789436032</v>
+        <v>712.9228174663466</v>
       </c>
       <c r="AE20" t="n">
-        <v>7.2</v>
+        <v>35.1</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -4140,63 +4140,63 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>87</v>
+        <v>3</v>
       </c>
       <c r="AL20" t="n">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="AM20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
         <v>4</v>
       </c>
-      <c r="AN20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1640584</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>3936339</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>4899099</v>
+        <v>23461577</v>
       </c>
       <c r="AV20" t="n">
-        <v>4899099</v>
+        <v>23461577</v>
       </c>
       <c r="AW20" t="n">
-        <v>6295322</v>
+        <v>23461577</v>
       </c>
       <c r="AX20" t="n">
-        <v>1640584</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>4899099</v>
+        <v>23461577</v>
       </c>
       <c r="AZ20" t="n">
         <v>1</v>
@@ -4205,18 +4205,18 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0.3349</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -4228,160 +4228,160 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H21" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>596.7</v>
+        <v>153.1</v>
       </c>
       <c r="J21" t="n">
-        <v>589.6</v>
+        <v>100.9</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2</v>
+        <v>51.7</v>
       </c>
       <c r="L21" t="n">
-        <v>64.68000000000001</v>
+        <v>69.56</v>
       </c>
       <c r="M21" t="n">
-        <v>5.62</v>
+        <v>3.01</v>
       </c>
       <c r="N21" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0.505</v>
+        <v>0.191</v>
       </c>
       <c r="Q21" t="n">
-        <v>1112</v>
+        <v>1577</v>
       </c>
       <c r="R21" t="n">
-        <v>56.6</v>
+        <v>55</v>
       </c>
       <c r="S21" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.11</v>
+        <v>22</v>
       </c>
       <c r="U21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="W21" t="n">
-        <v>1.58</v>
+        <v>5.28</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="Y21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>-110</v>
+        <v>5</v>
       </c>
       <c r="AA21" t="n">
-        <v>574.46</v>
+        <v>124.35</v>
       </c>
       <c r="AB21" t="n">
-        <v>510.05</v>
+        <v>115.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>15.4</v>
+        <v>42</v>
       </c>
       <c r="AD21" t="n">
-        <v>578.7647399321921</v>
+        <v>100.8969543402749</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.1</v>
+        <v>51.7</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>10-06-2026</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="AK21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>89</v>
+      </c>
+      <c r="AM21" t="n">
         <v>88</v>
       </c>
-      <c r="AL21" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>7</v>
-      </c>
       <c r="AN21" t="n">
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>12904187</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>19212594</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>19212594</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>49465328</v>
+        <v>30063761</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>19212594</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -4393,12 +4393,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -4410,160 +4410,160 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F22" t="n">
+        <v>15</v>
+      </c>
+      <c r="G22" t="n">
+        <v>25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>596.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>589.6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L22" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="N22" t="n">
+        <v>40</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>1120</v>
+      </c>
+      <c r="R22" t="n">
+        <v>57</v>
+      </c>
+      <c r="S22" t="n">
+        <v>21</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U22" t="n">
+        <v>23</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-110</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>574.46</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>510.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>578.7647399321921</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>04-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>88</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
         <v>11</v>
       </c>
-      <c r="G22" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>153.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="K22" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="L22" t="n">
-        <v>69.56</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="AP22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>33</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>12904187</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>19212594</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>19212594</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>49465328</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>19212594</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>2</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>11-06-2026</t>
-        </is>
-      </c>
-      <c r="P22" t="n">
-        <v>0.183</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1646</v>
-      </c>
-      <c r="R22" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="S22" t="n">
-        <v>7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>22</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W22" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="Y22" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>124.35</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>115.55</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>100.8969543402749</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>10-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>11-06-2026</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>89</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>88</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>30063761</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0.576</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="Q23" t="n">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="R23" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="S23" t="n">
         <v>22</v>
@@ -4757,12 +4757,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -4777,89 +4777,93 @@
         <v>25</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H24" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="I24" t="n">
-        <v>14.1</v>
+        <v>1142.2</v>
       </c>
       <c r="J24" t="n">
-        <v>12.47</v>
+        <v>1173.96</v>
       </c>
       <c r="K24" t="n">
-        <v>13.1</v>
+        <v>-2.7</v>
       </c>
       <c r="L24" t="n">
-        <v>69.12</v>
+        <v>69.75</v>
       </c>
       <c r="M24" t="n">
-        <v>1.64</v>
+        <v>59.58</v>
       </c>
       <c r="N24" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.412</v>
+        <v>2.213</v>
       </c>
       <c r="Q24" t="n">
-        <v>398</v>
+        <v>2692</v>
       </c>
       <c r="R24" t="n">
-        <v>1282</v>
+        <v>211</v>
       </c>
       <c r="S24" t="n">
-        <v>-61</v>
-      </c>
-      <c r="T24" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="T24" t="n">
+        <v>19.05</v>
+      </c>
       <c r="U24" t="n">
-        <v>-98</v>
+        <v>194</v>
       </c>
       <c r="V24" t="n">
-        <v>0.01</v>
+        <v>1.03</v>
       </c>
       <c r="W24" t="n">
-        <v>2.46</v>
+        <v>3.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0.44</v>
+        <v>0.06</v>
       </c>
       <c r="Y24" t="b">
         <v>1</v>
       </c>
-      <c r="Z24" t="inlineStr"/>
+      <c r="Z24" t="n">
+        <v>3.87</v>
+      </c>
       <c r="AA24" t="n">
-        <v>11.38</v>
+        <v>1168.37</v>
       </c>
       <c r="AB24" t="n">
-        <v>13.43</v>
+        <v>1086.85</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.8</v>
+        <v>12.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>12.43442394576657</v>
+        <v>1173.964532439025</v>
       </c>
       <c r="AE24" t="n">
-        <v>13.4</v>
+        <v>-2.7</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -4869,58 +4873,58 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>10-08-2026</t>
+          <t>25-06-2026</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="AL24" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="AM24" t="n">
+        <v>31</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>3</v>
       </c>
-      <c r="AN24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>17</v>
-      </c>
       <c r="AR24" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="AS24" t="n">
-        <v>1756804</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>5734082</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>16959087</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>16959087</v>
+        <v>586966134</v>
       </c>
       <c r="AW24" t="n">
-        <v>16959087</v>
+        <v>595794044</v>
       </c>
       <c r="AX24" t="n">
-        <v>1756804</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>16959087</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
         <v>1</v>
@@ -4929,18 +4933,18 @@
         <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>0.1036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -4955,93 +4959,89 @@
         <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="G25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H25" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="I25" t="n">
-        <v>1142.2</v>
+        <v>14.1</v>
       </c>
       <c r="J25" t="n">
-        <v>1173.96</v>
+        <v>12.52</v>
       </c>
       <c r="K25" t="n">
-        <v>-2.7</v>
+        <v>12.6</v>
       </c>
       <c r="L25" t="n">
-        <v>69.75</v>
+        <v>69.12</v>
       </c>
       <c r="M25" t="n">
-        <v>59.58</v>
+        <v>1.69</v>
       </c>
       <c r="N25" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.178</v>
+        <v>0.427</v>
       </c>
       <c r="Q25" t="n">
-        <v>2735</v>
+        <v>396</v>
       </c>
       <c r="R25" t="n">
-        <v>214</v>
+        <v>1279</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
-      </c>
-      <c r="T25" t="n">
-        <v>19.05</v>
-      </c>
+        <v>-61</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
       <c r="U25" t="n">
-        <v>194</v>
+        <v>-98</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>0.01</v>
       </c>
       <c r="W25" t="n">
-        <v>3.08</v>
+        <v>2.46</v>
       </c>
       <c r="X25" t="n">
-        <v>0.06</v>
+        <v>0.44</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
       </c>
-      <c r="Z25" t="n">
-        <v>3.87</v>
-      </c>
+      <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="n">
-        <v>1168.37</v>
+        <v>11.38</v>
       </c>
       <c r="AB25" t="n">
-        <v>1086.85</v>
+        <v>13.43</v>
       </c>
       <c r="AC25" t="n">
-        <v>12.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1173.964532439025</v>
+        <v>12.47706136306301</v>
       </c>
       <c r="AE25" t="n">
-        <v>-2.7</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -5051,58 +5051,58 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25-06-2026</t>
+          <t>10-08-2026</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="AL25" t="n">
-        <v>74</v>
+        <v>28</v>
       </c>
       <c r="AM25" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ25" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2305804</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>6283082</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>17508087</v>
       </c>
       <c r="AV25" t="n">
-        <v>586966134</v>
+        <v>17508087</v>
       </c>
       <c r="AW25" t="n">
-        <v>595794044</v>
+        <v>17508087</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>2305804</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>17508087</v>
       </c>
       <c r="AZ25" t="n">
         <v>1</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>0.1317</v>
       </c>
     </row>
     <row r="26">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -5172,7 +5172,7 @@
         <v>0.102</v>
       </c>
       <c r="Q26" t="n">
-        <v>1716</v>
+        <v>1713</v>
       </c>
       <c r="R26" t="n">
         <v>20.3</v>
@@ -5349,13 +5349,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.916</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="Q27" t="n">
-        <v>5281</v>
+        <v>5172</v>
       </c>
       <c r="R27" t="n">
-        <v>42.4</v>
+        <v>41.5</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5531,13 +5531,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0.389</v>
+        <v>0.392</v>
       </c>
       <c r="Q28" t="n">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="R28" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="S28" t="n">
         <v>246</v>
@@ -5661,12 +5661,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -5678,87 +5678,87 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F29" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="H29" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>132.78</v>
+        <v>328.8</v>
       </c>
       <c r="J29" t="n">
-        <v>83.06</v>
+        <v>297.3</v>
       </c>
       <c r="K29" t="n">
-        <v>59.9</v>
+        <v>10.6</v>
       </c>
       <c r="L29" t="n">
-        <v>72.53</v>
+        <v>67.69</v>
       </c>
       <c r="M29" t="n">
-        <v>0.42</v>
+        <v>2.97</v>
       </c>
       <c r="N29" t="n">
         <v>1</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.046</v>
+        <v>0.267</v>
       </c>
       <c r="Q29" t="n">
-        <v>917</v>
+        <v>1113</v>
       </c>
       <c r="R29" t="n">
-        <v>98</v>
+        <v>19.8</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T29" t="n">
-        <v>1.43</v>
+        <v>29</v>
       </c>
       <c r="U29" t="n">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="V29" t="n">
-        <v>0.34</v>
+        <v>4.07</v>
       </c>
       <c r="W29" t="n">
-        <v>9.710000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.67</v>
+        <v>17</v>
       </c>
       <c r="AA29" t="n">
-        <v>110.46</v>
+        <v>334.88</v>
       </c>
       <c r="AB29" t="n">
-        <v>70.91</v>
+        <v>346.36</v>
       </c>
       <c r="AC29" t="n">
-        <v>156</v>
+        <v>2.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>83.06001984126983</v>
+        <v>297.30147</v>
       </c>
       <c r="AE29" t="n">
-        <v>59.9</v>
+        <v>10.6</v>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
@@ -5777,22 +5777,22 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AM29" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="AN29" t="n">
         <v>0</v>
@@ -5822,7 +5822,7 @@
         <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>4186225</v>
+        <v>29730147</v>
       </c>
       <c r="AX29" t="n">
         <v>0</v>
@@ -5843,12 +5843,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -5860,87 +5860,87 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F30" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="I30" t="n">
-        <v>328.8</v>
+        <v>132.78</v>
       </c>
       <c r="J30" t="n">
-        <v>297.3</v>
+        <v>83.06</v>
       </c>
       <c r="K30" t="n">
-        <v>10.6</v>
+        <v>59.9</v>
       </c>
       <c r="L30" t="n">
-        <v>67.69</v>
+        <v>72.53</v>
       </c>
       <c r="M30" t="n">
-        <v>2.97</v>
+        <v>0.42</v>
       </c>
       <c r="N30" t="n">
         <v>1</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.268</v>
+        <v>0.048</v>
       </c>
       <c r="Q30" t="n">
-        <v>1107</v>
+        <v>871</v>
       </c>
       <c r="R30" t="n">
-        <v>19.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T30" t="n">
-        <v>29</v>
+        <v>1.43</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="V30" t="n">
-        <v>4.07</v>
+        <v>0.34</v>
       </c>
       <c r="W30" t="n">
-        <v>11.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>17</v>
+        <v>3.67</v>
       </c>
       <c r="AA30" t="n">
-        <v>334.88</v>
+        <v>110.46</v>
       </c>
       <c r="AB30" t="n">
-        <v>346.36</v>
+        <v>70.91</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.4</v>
+        <v>156</v>
       </c>
       <c r="AD30" t="n">
-        <v>297.30147</v>
+        <v>83.06001984126983</v>
       </c>
       <c r="AE30" t="n">
-        <v>10.6</v>
+        <v>59.9</v>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
@@ -5959,22 +5959,22 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="AM30" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="AN30" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>29730147</v>
+        <v>4186225</v>
       </c>
       <c r="AX30" t="n">
         <v>0</v>
@@ -6025,12 +6025,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -6042,177 +6042,177 @@
         </is>
       </c>
       <c r="E31" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" t="n">
         <v>12</v>
       </c>
-      <c r="F31" t="n">
-        <v>30</v>
-      </c>
       <c r="G31" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>1282.8</v>
+        <v>198.33</v>
       </c>
       <c r="J31" t="n">
-        <v>1104.34</v>
+        <v>191.87</v>
       </c>
       <c r="K31" t="n">
-        <v>16.2</v>
+        <v>3.4</v>
       </c>
       <c r="L31" t="n">
-        <v>60.82</v>
+        <v>70.02</v>
       </c>
       <c r="M31" t="n">
-        <v>5.22</v>
+        <v>1.34</v>
       </c>
       <c r="N31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.002</v>
+        <v>0.039</v>
       </c>
       <c r="Q31" t="n">
-        <v>347948</v>
+        <v>3468</v>
       </c>
       <c r="R31" t="n">
-        <v>19.1</v>
+        <v>20.6</v>
       </c>
       <c r="S31" t="n">
+        <v>-4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>51</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-9</v>
+      </c>
+      <c r="V31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="Y31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>214.03</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>194.65</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>191.8684857142857</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Early Accumulation</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL31" t="n">
         <v>7</v>
       </c>
-      <c r="T31" t="n">
-        <v>4158</v>
-      </c>
-      <c r="U31" t="n">
-        <v>44</v>
-      </c>
-      <c r="V31" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="W31" t="n">
-        <v>53.4</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="Y31" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1270.1</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1388.66</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>-6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1104.337889591841</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>16.2</v>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>12-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>12-06-2026</t>
-        </is>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>87</v>
-      </c>
       <c r="AM31" t="n">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>11966478</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="AW31" t="n">
-        <v>52192113</v>
+        <v>13430794</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>11966478</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>13430794</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA31" t="n">
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>0.891</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -6224,166 +6224,166 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>198.33</v>
+        <v>1282.8</v>
       </c>
       <c r="J32" t="n">
-        <v>191.87</v>
+        <v>1104.34</v>
       </c>
       <c r="K32" t="n">
-        <v>3.4</v>
+        <v>16.2</v>
       </c>
       <c r="L32" t="n">
-        <v>70.02</v>
+        <v>60.82</v>
       </c>
       <c r="M32" t="n">
-        <v>1.34</v>
+        <v>5.22</v>
       </c>
       <c r="N32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0.038</v>
+        <v>0.002</v>
       </c>
       <c r="Q32" t="n">
-        <v>3485</v>
+        <v>346332</v>
       </c>
       <c r="R32" t="n">
-        <v>20.7</v>
+        <v>19</v>
       </c>
       <c r="S32" t="n">
-        <v>-4</v>
+        <v>7</v>
       </c>
       <c r="T32" t="n">
-        <v>51</v>
+        <v>4158</v>
       </c>
       <c r="U32" t="n">
-        <v>-9</v>
+        <v>44</v>
       </c>
       <c r="V32" t="n">
-        <v>2.04</v>
+        <v>25.89</v>
       </c>
       <c r="W32" t="n">
-        <v>20.8</v>
+        <v>53.4</v>
       </c>
       <c r="X32" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="Y32" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z32" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AA32" t="n">
-        <v>214.03</v>
+        <v>1270.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>194.65</v>
+        <v>1388.66</v>
       </c>
       <c r="AC32" t="n">
-        <v>38.1</v>
+        <v>-6</v>
       </c>
       <c r="AD32" t="n">
-        <v>191.8684857142857</v>
+        <v>1104.337889591841</v>
       </c>
       <c r="AE32" t="n">
-        <v>3.4</v>
+        <v>16.2</v>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>Early Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
       <c r="AK32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="AM32" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="AN32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS32" t="n">
-        <v>11966478</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>13430794</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>13430794</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>13430794</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>13430794</v>
+        <v>52192113</v>
       </c>
       <c r="AX32" t="n">
-        <v>11966478</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>13430794</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA32" t="n">
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0.891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -6441,13 +6441,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="Q33" t="n">
-        <v>5030</v>
+        <v>5171</v>
       </c>
       <c r="R33" t="n">
-        <v>32.8</v>
+        <v>33.7</v>
       </c>
       <c r="S33" t="n">
         <v>-25</v>
@@ -6626,10 +6626,10 @@
         <v>0.052</v>
       </c>
       <c r="Q34" t="n">
-        <v>2070</v>
+        <v>2067</v>
       </c>
       <c r="R34" t="n">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -6805,13 +6805,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="Q35" t="n">
-        <v>3262</v>
+        <v>3223</v>
       </c>
       <c r="R35" t="n">
-        <v>22.1</v>
+        <v>21.8</v>
       </c>
       <c r="S35" t="n">
         <v>17</v>
@@ -6987,13 +6987,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0.149</v>
+        <v>0.147</v>
       </c>
       <c r="Q36" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="R36" t="n">
-        <v>24.1</v>
+        <v>24.4</v>
       </c>
       <c r="S36" t="n">
         <v>12</v>
@@ -7117,16 +7117,16 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -7137,176 +7137,178 @@
         <v>20</v>
       </c>
       <c r="F37" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G37" t="n">
+        <v>10</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>484.5</v>
+      </c>
+      <c r="J37" t="n">
+        <v>489.56</v>
+      </c>
+      <c r="K37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>75</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4.84</v>
+      </c>
+      <c r="N37" t="n">
         <v>5</v>
       </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>776.55</v>
-      </c>
-      <c r="J37" t="n">
-        <v>815.16</v>
-      </c>
-      <c r="K37" t="n">
-        <v>-4.7</v>
-      </c>
-      <c r="L37" t="n">
-        <v>73.2</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3</v>
-      </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.158</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="Q37" t="n">
-        <v>786</v>
+        <v>56219</v>
       </c>
       <c r="R37" t="n">
-        <v>14.3</v>
+        <v>47.6</v>
       </c>
       <c r="S37" t="n">
-        <v>185</v>
+        <v>5</v>
       </c>
       <c r="T37" t="n">
-        <v>11.55</v>
+        <v>562</v>
       </c>
       <c r="U37" t="n">
-        <v>204</v>
+        <v>8</v>
       </c>
       <c r="V37" t="n">
-        <v>6.84</v>
+        <v>3.16</v>
       </c>
       <c r="W37" t="n">
-        <v>50.7</v>
+        <v>22.9</v>
       </c>
       <c r="X37" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Y37" t="b">
         <v>1</v>
       </c>
       <c r="Z37" t="n">
-        <v>16.07</v>
+        <v>17</v>
       </c>
       <c r="AA37" t="n">
-        <v>740.6799999999999</v>
-      </c>
-      <c r="AB37" t="inlineStr"/>
+        <v>512.97</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>499.73</v>
+      </c>
       <c r="AC37" t="n">
-        <v>-14.6</v>
+        <v>10.4</v>
       </c>
       <c r="AD37" t="n">
-        <v>815.1570095913809</v>
+        <v>489.5623319654733</v>
       </c>
       <c r="AE37" t="n">
-        <v>-4.7</v>
+        <v>-1</v>
       </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG37" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AH37" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Early Accumulation</t>
         </is>
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>19-06-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AR37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>48436318</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>48436318</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>48436318</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>48436318</v>
       </c>
       <c r="AW37" t="n">
-        <v>12408320</v>
+        <v>48436318</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>48436318</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>48436318</v>
       </c>
       <c r="AZ37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -7317,98 +7319,96 @@
         <v>20</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>169.59</v>
+        <v>776.55</v>
       </c>
       <c r="J38" t="n">
-        <v>189.45</v>
+        <v>815.16</v>
       </c>
       <c r="K38" t="n">
-        <v>-10.5</v>
+        <v>-4.7</v>
       </c>
       <c r="L38" t="n">
-        <v>64.08</v>
+        <v>73.2</v>
       </c>
       <c r="M38" t="n">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.499</v>
+        <v>0.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>681</v>
+        <v>774</v>
       </c>
       <c r="R38" t="n">
-        <v>15</v>
+        <v>14.1</v>
       </c>
       <c r="S38" t="n">
-        <v>-1</v>
+        <v>185</v>
       </c>
       <c r="T38" t="n">
-        <v>21</v>
+        <v>11.55</v>
       </c>
       <c r="U38" t="n">
-        <v>45</v>
+        <v>204</v>
       </c>
       <c r="V38" t="n">
-        <v>3.1</v>
+        <v>6.84</v>
       </c>
       <c r="W38" t="n">
-        <v>19.3</v>
+        <v>50.7</v>
       </c>
       <c r="X38" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y38" t="b">
         <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>11</v>
+        <v>16.07</v>
       </c>
       <c r="AA38" t="n">
-        <v>174.19</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>197.24</v>
-      </c>
+        <v>740.6799999999999</v>
+      </c>
+      <c r="AB38" t="inlineStr"/>
       <c r="AC38" t="n">
-        <v>-8</v>
+        <v>-14.6</v>
       </c>
       <c r="AD38" t="n">
-        <v>189.4527941996654</v>
+        <v>815.1570095913809</v>
       </c>
       <c r="AE38" t="n">
-        <v>-10.5</v>
+        <v>-4.7</v>
       </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Fresh</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG38" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
@@ -7418,53 +7418,53 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="AK38" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="AL38" t="n">
         <v>80</v>
       </c>
       <c r="AM38" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="AN38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AS38" t="n">
-        <v>3009963</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
-        <v>8001009</v>
+        <v>0</v>
       </c>
       <c r="AU38" t="n">
-        <v>8001009</v>
+        <v>0</v>
       </c>
       <c r="AV38" t="n">
-        <v>8001009</v>
+        <v>0</v>
       </c>
       <c r="AW38" t="n">
-        <v>33968886</v>
+        <v>12408320</v>
       </c>
       <c r="AX38" t="n">
-        <v>3009963</v>
+        <v>0</v>
       </c>
       <c r="AY38" t="n">
-        <v>8001009</v>
+        <v>0</v>
       </c>
       <c r="AZ38" t="n">
         <v>2</v>
@@ -7473,22 +7473,22 @@
         <v>0</v>
       </c>
       <c r="BB38" t="n">
-        <v>0.3762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -7496,301 +7496,303 @@
         </is>
       </c>
       <c r="E39" t="n">
+        <v>20</v>
+      </c>
+      <c r="F39" t="n">
         <v>25</v>
       </c>
-      <c r="F39" t="n">
-        <v>5</v>
-      </c>
       <c r="G39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>424.1</v>
+        <v>169.59</v>
       </c>
       <c r="J39" t="n">
-        <v>474.82</v>
+        <v>189.45</v>
       </c>
       <c r="K39" t="n">
-        <v>-10.7</v>
+        <v>-10.5</v>
       </c>
       <c r="L39" t="n">
-        <v>70.55</v>
+        <v>64.08</v>
       </c>
       <c r="M39" t="n">
-        <v>10.22</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
         <v>5</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.281</v>
+        <v>0.498</v>
       </c>
       <c r="Q39" t="n">
-        <v>3641</v>
+        <v>683</v>
       </c>
       <c r="R39" t="n">
-        <v>25.5</v>
+        <v>15</v>
       </c>
       <c r="S39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>21</v>
+      </c>
+      <c r="U39" t="n">
+        <v>45</v>
+      </c>
+      <c r="V39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Y39" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>174.19</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>197.24</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>189.4527941996654</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>-10.5</v>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>Fresh</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>19-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>02-09-2026</t>
+        </is>
+      </c>
+      <c r="AK39" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="n">
         <v>2</v>
       </c>
-      <c r="T39" t="n">
-        <v>127</v>
-      </c>
-      <c r="U39" t="n">
-        <v>-14</v>
-      </c>
-      <c r="V39" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="W39" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="X39" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y39" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>445.04</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>433.28</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>12.7</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>474.9692297340662</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>-10.7</v>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>05-08-2026</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>12-08-2026</t>
-        </is>
-      </c>
-      <c r="AK39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>33</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
       <c r="AP39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AQ39" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AR39" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>3009963</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>8001009</v>
       </c>
       <c r="AU39" t="n">
-        <v>76204248</v>
+        <v>8001009</v>
       </c>
       <c r="AV39" t="n">
-        <v>183533810</v>
+        <v>8001009</v>
       </c>
       <c r="AW39" t="n">
-        <v>183533810</v>
+        <v>33968886</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>3009963</v>
       </c>
       <c r="AY39" t="n">
-        <v>76204248</v>
+        <v>8001009</v>
       </c>
       <c r="AZ39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA39" t="n">
         <v>0</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>0.3762</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Watchlist</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F40" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>170.31</v>
+        <v>424.1</v>
       </c>
       <c r="J40" t="n">
-        <v>182.69</v>
+        <v>474.82</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.8</v>
+        <v>-10.7</v>
       </c>
       <c r="L40" t="n">
-        <v>69.05</v>
+        <v>70.55</v>
       </c>
       <c r="M40" t="n">
-        <v>0.74</v>
+        <v>10.22</v>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0.127</v>
+        <v>0.285</v>
       </c>
       <c r="Q40" t="n">
-        <v>582</v>
+        <v>3589</v>
       </c>
       <c r="R40" t="n">
-        <v>13.8</v>
+        <v>25.1</v>
       </c>
       <c r="S40" t="n">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="T40" t="n">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="U40" t="n">
-        <v>82</v>
+        <v>-14</v>
       </c>
       <c r="V40" t="n">
-        <v>3.07</v>
+        <v>6.41</v>
       </c>
       <c r="W40" t="n">
-        <v>42.7</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="X40" t="n">
-        <v>0.35</v>
+        <v>1.05</v>
       </c>
       <c r="Y40" t="b">
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AA40" t="n">
-        <v>170.6</v>
-      </c>
-      <c r="AB40" t="inlineStr"/>
+        <v>445.04</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>433.28</v>
+      </c>
       <c r="AC40" t="n">
-        <v>-11.9</v>
+        <v>12.7</v>
       </c>
       <c r="AD40" t="n">
-        <v>182.6945759634963</v>
+        <v>474.9692297340662</v>
       </c>
       <c r="AE40" t="n">
-        <v>-6.8</v>
+        <v>-10.7</v>
       </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG40" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH40" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AL40" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="AM40" t="n">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="AN40" t="n">
         <v>0</v>
@@ -7799,13 +7801,13 @@
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AR40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AS40" t="n">
         <v>0</v>
@@ -7814,22 +7816,22 @@
         <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>76204248</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>183533810</v>
       </c>
       <c r="AW40" t="n">
-        <v>7447179</v>
+        <v>183533810</v>
       </c>
       <c r="AX40" t="n">
         <v>0</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>76204248</v>
       </c>
       <c r="AZ40" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA40" t="n">
         <v>0</v>
@@ -7841,12 +7843,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -7858,179 +7860,179 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F41" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G41" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>55.03</v>
+        <v>170.31</v>
       </c>
       <c r="J41" t="n">
-        <v>53.54</v>
+        <v>182.69</v>
       </c>
       <c r="K41" t="n">
-        <v>2.8</v>
+        <v>-6.8</v>
       </c>
       <c r="L41" t="n">
-        <v>67.23</v>
+        <v>69.05</v>
       </c>
       <c r="M41" t="n">
-        <v>2.07</v>
+        <v>0.74</v>
       </c>
       <c r="N41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.784</v>
+        <v>0.128</v>
       </c>
       <c r="Q41" t="n">
-        <v>116</v>
-      </c>
-      <c r="R41" t="inlineStr"/>
+        <v>577</v>
+      </c>
+      <c r="R41" t="n">
+        <v>13.7</v>
+      </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="T41" t="n">
-        <v>2.47</v>
+        <v>15</v>
       </c>
       <c r="U41" t="n">
-        <v>-3779</v>
+        <v>82</v>
       </c>
       <c r="V41" t="n">
-        <v>-0.05</v>
+        <v>3.07</v>
       </c>
       <c r="W41" t="n">
-        <v>-1.26</v>
+        <v>42.7</v>
       </c>
       <c r="X41" t="n">
-        <v>0.8</v>
+        <v>0.35</v>
       </c>
       <c r="Y41" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="AB41" t="inlineStr"/>
+      <c r="AC41" t="n">
+        <v>-11.9</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>182.6945759634963</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>-6.8</v>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
         <v>3</v>
       </c>
-      <c r="AA41" t="n">
-        <v>54.04</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>55.1</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>-8.300000000000001</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>53.53569858095489</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>Fresh</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Confirmed Accumulation</t>
-        </is>
-      </c>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>09-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>07-09-2026</t>
-        </is>
-      </c>
-      <c r="AK41" t="n">
-        <v>90</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>90</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO41" t="n">
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>7447179</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
         <v>3</v>
       </c>
-      <c r="AP41" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>769644</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>1889908</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>14844955</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>18404259</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>18404259</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>769644</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>14844955</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>2</v>
-      </c>
       <c r="BA41" t="n">
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0.0518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -8038,177 +8040,175 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F42" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H42" t="n">
         <v>-2</v>
       </c>
       <c r="I42" t="n">
-        <v>55.21</v>
+        <v>55.03</v>
       </c>
       <c r="J42" t="n">
-        <v>60.15</v>
+        <v>53.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="L42" t="n">
-        <v>73.01000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="M42" t="n">
-        <v>0.9</v>
+        <v>2.07</v>
       </c>
       <c r="N42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0.188</v>
+        <v>1.784</v>
       </c>
       <c r="Q42" t="n">
-        <v>479</v>
-      </c>
-      <c r="R42" t="n">
-        <v>12</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="R42" t="inlineStr"/>
       <c r="S42" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="T42" t="n">
-        <v>21</v>
+        <v>2.47</v>
       </c>
       <c r="U42" t="n">
-        <v>20</v>
+        <v>-3779</v>
       </c>
       <c r="V42" t="n">
-        <v>1.22</v>
+        <v>-0.05</v>
       </c>
       <c r="W42" t="n">
-        <v>12</v>
+        <v>-1.26</v>
       </c>
       <c r="X42" t="n">
-        <v>0.58</v>
+        <v>0.8</v>
       </c>
       <c r="Y42" t="b">
         <v>1</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA42" t="n">
-        <v>57.55</v>
+        <v>54.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>58.97</v>
+        <v>55.1</v>
       </c>
       <c r="AC42" t="n">
-        <v>-3.1</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD42" t="n">
-        <v>60.1322085106383</v>
+        <v>53.53569858095489</v>
       </c>
       <c r="AE42" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Aging</t>
+          <t>Fresh</t>
         </is>
       </c>
       <c r="AG42" t="inlineStr">
         <is>
-          <t>Mature Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>Mature — Wait for Pullback</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>05-08-2026</t>
+          <t>09-06-2026</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
       <c r="AK42" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="AL42" t="n">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="AM42" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP42" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AR42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AS42" t="n">
-        <v>0</v>
+        <v>769644</v>
       </c>
       <c r="AT42" t="n">
-        <v>0</v>
+        <v>1889908</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>14844955</v>
       </c>
       <c r="AV42" t="n">
-        <v>14131069</v>
+        <v>18404259</v>
       </c>
       <c r="AW42" t="n">
-        <v>14131069</v>
+        <v>18404259</v>
       </c>
       <c r="AX42" t="n">
-        <v>0</v>
+        <v>769644</v>
       </c>
       <c r="AY42" t="n">
-        <v>0</v>
+        <v>14844955</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA42" t="n">
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>0.0518</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -8223,118 +8223,118 @@
         <v>17</v>
       </c>
       <c r="F43" t="n">
+        <v>23</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I43" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="J43" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="L43" t="n">
+        <v>73.01000000000001</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>06-08-2026</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>475</v>
+      </c>
+      <c r="R43" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="S43" t="n">
+        <v>19</v>
+      </c>
+      <c r="T43" t="n">
         <v>21</v>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>262.05</v>
-      </c>
-      <c r="J43" t="n">
-        <v>269.7</v>
-      </c>
-      <c r="K43" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="L43" t="n">
-        <v>73.09</v>
-      </c>
-      <c r="M43" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="N43" t="n">
-        <v>1</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>24-06-2026</t>
-        </is>
-      </c>
-      <c r="P43" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1486</v>
-      </c>
-      <c r="R43" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S43" t="n">
-        <v>6</v>
-      </c>
-      <c r="T43" t="n">
-        <v>46</v>
-      </c>
       <c r="U43" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V43" t="n">
-        <v>4.31</v>
+        <v>1.22</v>
       </c>
       <c r="W43" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="X43" t="n">
-        <v>0.28</v>
+        <v>0.58</v>
       </c>
       <c r="Y43" t="b">
         <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="AA43" t="n">
-        <v>267.89</v>
+        <v>57.55</v>
       </c>
       <c r="AB43" t="n">
-        <v>291.87</v>
+        <v>58.97</v>
       </c>
       <c r="AC43" t="n">
-        <v>-1.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD43" t="n">
-        <v>269.7</v>
+        <v>60.1322085106383</v>
       </c>
       <c r="AE43" t="n">
-        <v>-2.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Aging</t>
         </is>
       </c>
       <c r="AG43" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Mature Accumulation</t>
         </is>
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Mature — Wait for Pullback</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>05-08-2026</t>
         </is>
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL43" t="n">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="AM43" t="n">
-        <v>75</v>
+        <v>32</v>
       </c>
       <c r="AN43" t="n">
         <v>0</v>
@@ -8346,10 +8346,10 @@
         <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS43" t="n">
         <v>0</v>
@@ -8361,10 +8361,10 @@
         <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>14131069</v>
       </c>
       <c r="AW43" t="n">
-        <v>14833500</v>
+        <v>14131069</v>
       </c>
       <c r="AX43" t="n">
         <v>0</v>
@@ -8385,16 +8385,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -8402,10 +8402,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F44" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -8414,106 +8414,106 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>85.8</v>
+        <v>262.05</v>
       </c>
       <c r="J44" t="n">
-        <v>95.54000000000001</v>
+        <v>269.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-10.2</v>
+        <v>-2.8</v>
       </c>
       <c r="L44" t="n">
-        <v>71.72</v>
+        <v>73.09</v>
       </c>
       <c r="M44" t="n">
-        <v>10.87</v>
+        <v>1.48</v>
       </c>
       <c r="N44" t="n">
+        <v>1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R44" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="S44" t="n">
         <v>6</v>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="T44" t="n">
+        <v>46</v>
+      </c>
+      <c r="U44" t="n">
+        <v>18</v>
+      </c>
+      <c r="V44" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="W44" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="Y44" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>267.89</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>291.87</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>269.7</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
         <is>
           <t>24-06-2026</t>
         </is>
       </c>
-      <c r="P44" t="n">
-        <v>0.611</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>1780</v>
-      </c>
-      <c r="R44" t="n">
-        <v>32.1</v>
-      </c>
-      <c r="S44" t="n">
-        <v>39</v>
-      </c>
-      <c r="T44" t="n">
-        <v>31</v>
-      </c>
-      <c r="U44" t="n">
-        <v>8</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="W44" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>90.84</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>180.75</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>-45.8</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>100.1307680244762</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>-14.3</v>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>08-06-2026</t>
-        </is>
-      </c>
       <c r="AJ44" t="inlineStr">
         <is>
           <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="AM44" t="n">
         <v>75</v>
@@ -8531,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AS44" t="n">
         <v>0</v>
@@ -8546,7 +8546,7 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>104093262</v>
+        <v>14833500</v>
       </c>
       <c r="AX44" t="n">
         <v>0</v>
@@ -8555,7 +8555,7 @@
         <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA44" t="n">
         <v>0</v>
@@ -8567,16 +8567,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -8584,113 +8584,121 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F45" t="n">
+        <v>10</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="J45" t="n">
+        <v>95.54000000000001</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-10.2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>71.72</v>
+      </c>
+      <c r="M45" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="N45" t="n">
+        <v>6</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0.611</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1778</v>
+      </c>
+      <c r="R45" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="S45" t="n">
+        <v>39</v>
+      </c>
+      <c r="T45" t="n">
+        <v>31</v>
+      </c>
+      <c r="U45" t="n">
+        <v>8</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="W45" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Y45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
         <v>9</v>
       </c>
-      <c r="G45" t="n">
-        <v>10</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>65.72</v>
-      </c>
-      <c r="J45" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L45" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="P45" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>806</v>
-      </c>
-      <c r="R45" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Y45" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>12.14</v>
-      </c>
       <c r="AA45" t="n">
-        <v>67.48</v>
-      </c>
-      <c r="AB45" t="inlineStr"/>
+        <v>90.84</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>180.75</v>
+      </c>
       <c r="AC45" t="n">
-        <v>29.7</v>
+        <v>-45.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>64.04438155136269</v>
+        <v>100.1307680244762</v>
       </c>
       <c r="AE45" t="n">
-        <v>2.6</v>
+        <v>-14.3</v>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG45" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL45" t="n">
-        <v>21</v>
+        <v>91</v>
       </c>
       <c r="AM45" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
       <c r="AN45" t="n">
         <v>0</v>
@@ -8699,10 +8707,10 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AQ45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AR45" t="n">
         <v>6</v>
@@ -8714,22 +8722,22 @@
         <v>0</v>
       </c>
       <c r="AU45" t="n">
-        <v>6109834</v>
+        <v>0</v>
       </c>
       <c r="AV45" t="n">
-        <v>6109834</v>
+        <v>0</v>
       </c>
       <c r="AW45" t="n">
-        <v>6109834</v>
+        <v>104093262</v>
       </c>
       <c r="AX45" t="n">
         <v>0</v>
       </c>
       <c r="AY45" t="n">
-        <v>6109834</v>
+        <v>0</v>
       </c>
       <c r="AZ45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA45" t="n">
         <v>0</v>
@@ -8741,16 +8749,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -8758,121 +8766,113 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>268.05</v>
+        <v>65.72</v>
       </c>
       <c r="J46" t="n">
-        <v>292.28</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-8.300000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="L46" t="n">
-        <v>70.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>1.29</v>
+        <v>0.31</v>
       </c>
       <c r="N46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.038</v>
       </c>
       <c r="Q46" t="n">
-        <v>1531</v>
+        <v>817</v>
       </c>
       <c r="R46" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S46" t="n">
-        <v>13</v>
-      </c>
+        <v>19.6</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Y46" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>67.48</v>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>64.04438155136269</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="AG46" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Confirmed Accumulation</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>17-08-2026</t>
+        </is>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
         <v>21</v>
       </c>
-      <c r="U46" t="n">
-        <v>-4</v>
-      </c>
-      <c r="V46" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="W46" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="Y46" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>294.14</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>319.32</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>297.217890625</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>Stale</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr">
-        <is>
-          <t>Stale Accumulation</t>
-        </is>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Late — Poor Entry</t>
-        </is>
-      </c>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>11-06-2026</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>16-06-2026</t>
-        </is>
-      </c>
-      <c r="AK46" t="n">
-        <v>5</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>88</v>
-      </c>
       <c r="AM46" t="n">
-        <v>83</v>
+        <v>21</v>
       </c>
       <c r="AN46" t="n">
         <v>0</v>
@@ -8881,10 +8881,10 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AR46" t="n">
         <v>6</v>
@@ -8896,22 +8896,22 @@
         <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>6109834</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>6109834</v>
       </c>
       <c r="AW46" t="n">
-        <v>19021945</v>
+        <v>6109834</v>
       </c>
       <c r="AX46" t="n">
         <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>6109834</v>
       </c>
       <c r="AZ46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BA46" t="n">
         <v>0</v>
@@ -8923,16 +8923,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -8940,10 +8940,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F47" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -8952,75 +8952,75 @@
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>171.96</v>
+        <v>268.05</v>
       </c>
       <c r="J47" t="n">
-        <v>174.99</v>
+        <v>292.28</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="M47" t="n">
-        <v>0.79</v>
+        <v>1.29</v>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0.041</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="Q47" t="n">
-        <v>1910</v>
+        <v>1523</v>
       </c>
       <c r="R47" t="n">
-        <v>20.2</v>
+        <v>19.3</v>
       </c>
       <c r="S47" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="T47" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="U47" t="n">
         <v>-4</v>
       </c>
       <c r="V47" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="W47" t="n">
-        <v>14.2</v>
+        <v>19.9</v>
       </c>
       <c r="X47" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="Y47" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AA47" t="n">
-        <v>182.92</v>
+        <v>294.14</v>
       </c>
       <c r="AB47" t="n">
-        <v>189.3</v>
+        <v>319.32</v>
       </c>
       <c r="AC47" t="n">
-        <v>-11.1</v>
+        <v>-7.2</v>
       </c>
       <c r="AD47" t="n">
-        <v>174.9865111111111</v>
+        <v>297.217890625</v>
       </c>
       <c r="AE47" t="n">
-        <v>-1.7</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="AF47" t="inlineStr">
         <is>
@@ -9039,22 +9039,22 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL47" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AM47" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
@@ -9069,7 +9069,7 @@
         <v>0</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AS47" t="n">
         <v>0</v>
@@ -9084,7 +9084,7 @@
         <v>0</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>19021945</v>
       </c>
       <c r="AX47" t="n">
         <v>0</v>
@@ -9093,7 +9093,7 @@
         <v>0</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA47" t="n">
         <v>0</v>
@@ -9105,16 +9105,16 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -9122,157 +9122,157 @@
         </is>
       </c>
       <c r="E48" t="n">
+        <v>17</v>
+      </c>
+      <c r="F48" t="n">
+        <v>14</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>171.96</v>
+      </c>
+      <c r="J48" t="n">
+        <v>174.99</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="L48" t="n">
+        <v>65.64</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="N48" t="n">
+        <v>1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>08-06-2026</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>1894</v>
+      </c>
+      <c r="R48" t="n">
         <v>20</v>
       </c>
-      <c r="F48" t="n">
-        <v>12</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="J48" t="n">
-        <v>34.64</v>
-      </c>
-      <c r="K48" t="n">
-        <v>-18.9</v>
-      </c>
-      <c r="L48" t="n">
-        <v>61.81</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="N48" t="n">
-        <v>11</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>24-08-2026</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>295</v>
-      </c>
-      <c r="R48" t="n">
-        <v>15.6</v>
-      </c>
       <c r="S48" t="n">
-        <v>16</v>
+        <v>-3</v>
       </c>
       <c r="T48" t="n">
-        <v>2.79</v>
+        <v>26</v>
       </c>
       <c r="U48" t="n">
-        <v>-30</v>
+        <v>-4</v>
       </c>
       <c r="V48" t="n">
-        <v>0.21</v>
+        <v>2.36</v>
       </c>
       <c r="W48" t="n">
-        <v>17.6</v>
+        <v>14.2</v>
       </c>
       <c r="X48" t="n">
-        <v>0.31</v>
+        <v>0.01</v>
       </c>
       <c r="Y48" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.83</v>
+        <v>36</v>
       </c>
       <c r="AA48" t="n">
-        <v>30.17</v>
+        <v>182.92</v>
       </c>
       <c r="AB48" t="n">
-        <v>32.93</v>
+        <v>189.3</v>
       </c>
       <c r="AC48" t="n">
-        <v>-2.4</v>
+        <v>-11.1</v>
       </c>
       <c r="AD48" t="n">
-        <v>34.64380341880342</v>
+        <v>174.9865111111111</v>
       </c>
       <c r="AE48" t="n">
-        <v>-18.9</v>
+        <v>-1.7</v>
       </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>Stale</t>
         </is>
       </c>
       <c r="AG48" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Stale Accumulation</t>
         </is>
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>Confirmed Accumulation</t>
+          <t>Late — Poor Entry</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>05-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="AK48" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="AM48" t="n">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="AN48" t="n">
         <v>0</v>
       </c>
       <c r="AO48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
         <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>743750</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>2202750</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>2202750</v>
+        <v>0</v>
       </c>
       <c r="AW48" t="n">
-        <v>7758579</v>
+        <v>0</v>
       </c>
       <c r="AX48" t="n">
         <v>0</v>
       </c>
       <c r="AY48" t="n">
-        <v>2202750</v>
+        <v>0</v>
       </c>
       <c r="AZ48" t="n">
         <v>1</v>
@@ -9287,27 +9287,27 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Avoid</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E49" t="n">
         <v>20</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -9316,145 +9316,145 @@
         <v>-2</v>
       </c>
       <c r="I49" t="n">
-        <v>82.78</v>
+        <v>28.08</v>
       </c>
       <c r="J49" t="n">
-        <v>102.08</v>
+        <v>34.64</v>
       </c>
       <c r="K49" t="n">
         <v>-18.9</v>
       </c>
       <c r="L49" t="n">
-        <v>71.89</v>
+        <v>61.81</v>
       </c>
       <c r="M49" t="n">
-        <v>0.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N49" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0.056</v>
+        <v>0.276</v>
       </c>
       <c r="Q49" t="n">
-        <v>845</v>
+        <v>294</v>
       </c>
       <c r="R49" t="n">
-        <v>23</v>
+        <v>15.5</v>
       </c>
       <c r="S49" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="T49" t="n">
-        <v>18.68</v>
+        <v>2.79</v>
       </c>
       <c r="U49" t="n">
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="V49" t="n">
-        <v>0.85</v>
+        <v>0.21</v>
       </c>
       <c r="W49" t="n">
-        <v>6.79</v>
+        <v>17.6</v>
       </c>
       <c r="X49" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="Y49" t="b">
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>4.02</v>
+        <v>1.83</v>
       </c>
       <c r="AA49" t="n">
-        <v>90.2</v>
+        <v>30.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>103.1</v>
+        <v>32.93</v>
       </c>
       <c r="AC49" t="n">
-        <v>-20.8</v>
+        <v>-2.4</v>
       </c>
       <c r="AD49" t="n">
-        <v>102.083871947252</v>
+        <v>34.64380341880342</v>
       </c>
       <c r="AE49" t="n">
         <v>-18.9</v>
       </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Stale</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="AG49" t="inlineStr">
         <is>
-          <t>Stale Accumulation</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>Late — Poor Entry</t>
+          <t>Confirmed Accumulation</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>05-06-2026</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>30-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="AK49" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>94</v>
+      </c>
+      <c r="AM49" t="n">
         <v>14</v>
       </c>
-      <c r="AL49" t="n">
-        <v>83</v>
-      </c>
-      <c r="AM49" t="n">
-        <v>69</v>
-      </c>
       <c r="AN49" t="n">
         <v>0</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR49" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AS49" t="n">
         <v>0</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>743750</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>2202750</v>
       </c>
       <c r="AV49" t="n">
-        <v>0</v>
+        <v>2202750</v>
       </c>
       <c r="AW49" t="n">
-        <v>4706679</v>
+        <v>7758579</v>
       </c>
       <c r="AX49" t="n">
         <v>0</v>
       </c>
       <c r="AY49" t="n">
-        <v>0</v>
+        <v>2202750</v>
       </c>
       <c r="AZ49" t="n">
         <v>1</v>
@@ -9463,6 +9463,188 @@
         <v>0</v>
       </c>
       <c r="BB49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WCIL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>26</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Avoid</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>20</v>
+      </c>
+      <c r="F50" t="n">
+        <v>8</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I50" t="n">
+        <v>82.78</v>
+      </c>
+      <c r="J50" t="n">
+        <v>102.08</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="L50" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="N50" t="n">
+        <v>4</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>836</v>
+      </c>
+      <c r="R50" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="S50" t="n">
+        <v>9</v>
+      </c>
+      <c r="T50" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="U50" t="n">
+        <v>-36</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="W50" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Y50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>4.02</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>-20.8</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>102.083871947252</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>Stale</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>Stale Accumulation</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Late — Poor Entry</t>
+        </is>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>16-06-2026</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="AK50" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>83</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>69</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>4706679</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -9477,7 +9659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9546,7 +9728,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gandhar Oil Refinery (India) Limited</t>
+          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9646,31 +9828,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CONFIPET</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CONFIDENCE PETROLEUM INDIA LIMITED</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>82.18000000000001</v>
+        <v>319.85</v>
       </c>
       <c r="D5" t="n">
-        <v>72.78</v>
+        <v>217.8</v>
       </c>
       <c r="E5" t="n">
-        <v>12.9</v>
+        <v>46.9</v>
       </c>
       <c r="F5" t="n">
-        <v>61.32</v>
+        <v>71.75</v>
       </c>
       <c r="G5" t="n">
-        <v>82.39</v>
+        <v>0.82</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -9681,31 +9863,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>CONFIPET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>CONFIDENCE PETROLEUM INDIA LIMITED</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>319.85</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>217.8</v>
+        <v>72.78</v>
       </c>
       <c r="E6" t="n">
-        <v>46.9</v>
+        <v>12.9</v>
       </c>
       <c r="F6" t="n">
-        <v>71.75</v>
+        <v>61.32</v>
       </c>
       <c r="G6" t="n">
-        <v>0.82</v>
+        <v>82.39</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -9751,175 +9933,175 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SIGIND</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Signet Industries Limited</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>66.91</v>
+        <v>202.13</v>
       </c>
       <c r="D8" t="n">
-        <v>70.34999999999999</v>
+        <v>164.1</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.9</v>
+        <v>23.2</v>
       </c>
       <c r="F8" t="n">
-        <v>72.56999999999999</v>
+        <v>60.6</v>
       </c>
       <c r="G8" t="n">
-        <v>1.04</v>
+        <v>0.25</v>
       </c>
       <c r="H8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>28-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>SIGIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Signet Industries Limited</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>202.13</v>
+        <v>66.91</v>
       </c>
       <c r="D9" t="n">
-        <v>164.1</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>23.2</v>
+        <v>-4.9</v>
       </c>
       <c r="F9" t="n">
-        <v>60.6</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="G9" t="n">
-        <v>0.25</v>
+        <v>1.04</v>
       </c>
       <c r="H9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>28-08-2026</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHEMBONDCH</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHEMBOND CHEMICALS LIMITED</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>267.15</v>
+        <v>108.05</v>
       </c>
       <c r="D10" t="n">
-        <v>243.52</v>
+        <v>91.7</v>
       </c>
       <c r="E10" t="n">
-        <v>9.699999999999999</v>
+        <v>17.8</v>
       </c>
       <c r="F10" t="n">
-        <v>67.65000000000001</v>
+        <v>70.88</v>
       </c>
       <c r="G10" t="n">
-        <v>1.11</v>
+        <v>8.49</v>
       </c>
       <c r="H10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>25-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>108.05</v>
+        <v>391.15</v>
       </c>
       <c r="D11" t="n">
-        <v>91.7</v>
+        <v>338.1</v>
       </c>
       <c r="E11" t="n">
-        <v>17.8</v>
+        <v>15.7</v>
       </c>
       <c r="F11" t="n">
-        <v>70.88</v>
+        <v>66.73</v>
       </c>
       <c r="G11" t="n">
-        <v>8.49</v>
+        <v>0.34</v>
       </c>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>CHEMBONDCH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>CHEMBOND CHEMICALS LIMITED</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>391.15</v>
+        <v>267.15</v>
       </c>
       <c r="D12" t="n">
-        <v>338.1</v>
+        <v>243.52</v>
       </c>
       <c r="E12" t="n">
-        <v>15.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>66.73</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>0.34</v>
+        <v>1.11</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>25-08-2026</t>
         </is>
       </c>
     </row>
@@ -10031,245 +10213,245 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>531.6</v>
+        <v>121.75</v>
       </c>
       <c r="D16" t="n">
-        <v>482.22</v>
+        <v>113.51</v>
       </c>
       <c r="E16" t="n">
-        <v>10.2</v>
+        <v>7.3</v>
       </c>
       <c r="F16" t="n">
-        <v>62.09</v>
+        <v>73.48</v>
       </c>
       <c r="G16" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>19.63</v>
+        <v>531.6</v>
       </c>
       <c r="D17" t="n">
-        <v>21.01</v>
+        <v>482.22</v>
       </c>
       <c r="E17" t="n">
-        <v>-6.6</v>
+        <v>10.2</v>
       </c>
       <c r="F17" t="n">
-        <v>70.87</v>
+        <v>62.09</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="H17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CHEMBOND</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>184.4</v>
+        <v>19.63</v>
       </c>
       <c r="D18" t="n">
-        <v>170.45</v>
+        <v>21.01</v>
       </c>
       <c r="E18" t="n">
-        <v>8.199999999999999</v>
+        <v>-6.6</v>
       </c>
       <c r="F18" t="n">
-        <v>67.54000000000001</v>
+        <v>70.87</v>
       </c>
       <c r="G18" t="n">
-        <v>0.26</v>
+        <v>0.5</v>
       </c>
       <c r="H18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>CHEMBOND</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>CHEMBOND MATERIAL TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>963.15</v>
+        <v>184.4</v>
       </c>
       <c r="D19" t="n">
-        <v>717.77</v>
+        <v>170.45</v>
       </c>
       <c r="E19" t="n">
-        <v>34.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>61.71</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>1.61</v>
+        <v>0.26</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>03-09-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>121.75</v>
+        <v>963.15</v>
       </c>
       <c r="D20" t="n">
-        <v>113.51</v>
+        <v>717.77</v>
       </c>
       <c r="E20" t="n">
-        <v>7.3</v>
+        <v>34.2</v>
       </c>
       <c r="F20" t="n">
-        <v>73.48</v>
+        <v>61.71</v>
       </c>
       <c r="G20" t="n">
-        <v>0.72</v>
+        <v>1.61</v>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>03-09-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>596.7</v>
+        <v>153.1</v>
       </c>
       <c r="D21" t="n">
-        <v>589.6</v>
+        <v>100.9</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2</v>
+        <v>51.7</v>
       </c>
       <c r="F21" t="n">
-        <v>64.68000000000001</v>
+        <v>69.56</v>
       </c>
       <c r="G21" t="n">
-        <v>5.62</v>
+        <v>3.01</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>153.1</v>
+        <v>596.7</v>
       </c>
       <c r="D22" t="n">
-        <v>100.9</v>
+        <v>589.6</v>
       </c>
       <c r="E22" t="n">
-        <v>51.7</v>
+        <v>1.2</v>
       </c>
       <c r="F22" t="n">
-        <v>69.56</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>3.01</v>
+        <v>5.62</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
@@ -10311,70 +10493,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AVONMORE</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>14.1</v>
+        <v>1142.2</v>
       </c>
       <c r="D24" t="n">
-        <v>12.47</v>
+        <v>1173.96</v>
       </c>
       <c r="E24" t="n">
-        <v>13.1</v>
+        <v>-2.7</v>
       </c>
       <c r="F24" t="n">
-        <v>69.12</v>
+        <v>69.75</v>
       </c>
       <c r="G24" t="n">
-        <v>1.64</v>
+        <v>59.58</v>
       </c>
       <c r="H24" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>04-09-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>AVONMORE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>AVONMORE CAPITAL &amp; MANAGEMENT SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1142.2</v>
+        <v>14.1</v>
       </c>
       <c r="D25" t="n">
-        <v>1173.96</v>
+        <v>12.52</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7</v>
+        <v>12.6</v>
       </c>
       <c r="F25" t="n">
-        <v>69.75</v>
+        <v>69.12</v>
       </c>
       <c r="G25" t="n">
-        <v>59.58</v>
+        <v>1.69</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>
@@ -10386,7 +10568,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PNGS REVA DIAMOND JEWELLERY LIMITED</t>
+          <t>PNGS Reva Diamond Jewellery Limited</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -10486,140 +10668,140 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>BAJAJHCARE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>BAJAJ HEALTHCARE LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>132.78</v>
+        <v>328.8</v>
       </c>
       <c r="D29" t="n">
-        <v>83.06</v>
+        <v>297.3</v>
       </c>
       <c r="E29" t="n">
-        <v>59.9</v>
+        <v>10.6</v>
       </c>
       <c r="F29" t="n">
-        <v>72.53</v>
+        <v>67.69</v>
       </c>
       <c r="G29" t="n">
-        <v>0.42</v>
+        <v>2.97</v>
       </c>
       <c r="H29" t="n">
         <v>1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAJAJHCARE</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BAJAJ HEALTHCARE LIMITED</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>328.8</v>
+        <v>132.78</v>
       </c>
       <c r="D30" t="n">
-        <v>297.3</v>
+        <v>83.06</v>
       </c>
       <c r="E30" t="n">
-        <v>10.6</v>
+        <v>59.9</v>
       </c>
       <c r="F30" t="n">
-        <v>67.69</v>
+        <v>72.53</v>
       </c>
       <c r="G30" t="n">
-        <v>2.97</v>
+        <v>0.42</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>HCL Technologies Limited</t>
+          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1282.8</v>
+        <v>198.33</v>
       </c>
       <c r="D31" t="n">
-        <v>1104.34</v>
+        <v>191.87</v>
       </c>
       <c r="E31" t="n">
-        <v>16.2</v>
+        <v>3.4</v>
       </c>
       <c r="F31" t="n">
-        <v>60.82</v>
+        <v>70.02</v>
       </c>
       <c r="G31" t="n">
-        <v>5.22</v>
+        <v>1.34</v>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>12-06-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ENVIRO INFRA ENGINEERS LIMITED</t>
+          <t>HCL Technologies Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>198.33</v>
+        <v>1282.8</v>
       </c>
       <c r="D32" t="n">
-        <v>191.87</v>
+        <v>1104.34</v>
       </c>
       <c r="E32" t="n">
-        <v>3.4</v>
+        <v>16.2</v>
       </c>
       <c r="F32" t="n">
-        <v>70.02</v>
+        <v>60.82</v>
       </c>
       <c r="G32" t="n">
-        <v>1.34</v>
+        <v>5.22</v>
       </c>
       <c r="H32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>12-06-2026</t>
         </is>
       </c>
     </row>
@@ -10766,276 +10948,276 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>BERGER PAINTS (I) LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>776.55</v>
+        <v>484.5</v>
       </c>
       <c r="D37" t="n">
-        <v>815.16</v>
+        <v>489.56</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.7</v>
+        <v>-1</v>
       </c>
       <c r="F37" t="n">
-        <v>73.2</v>
+        <v>75</v>
       </c>
       <c r="G37" t="n">
-        <v>1.24</v>
+        <v>4.84</v>
       </c>
       <c r="H37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>GANESHCP</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>169.59</v>
+        <v>776.55</v>
       </c>
       <c r="D38" t="n">
-        <v>189.45</v>
+        <v>815.16</v>
       </c>
       <c r="E38" t="n">
-        <v>-10.5</v>
+        <v>-4.7</v>
       </c>
       <c r="F38" t="n">
-        <v>64.08</v>
+        <v>73.2</v>
       </c>
       <c r="G38" t="n">
-        <v>3.4</v>
+        <v>1.24</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>GANESHCP</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>424.1</v>
+        <v>169.59</v>
       </c>
       <c r="D39" t="n">
-        <v>474.82</v>
+        <v>189.45</v>
       </c>
       <c r="E39" t="n">
-        <v>-10.7</v>
+        <v>-10.5</v>
       </c>
       <c r="F39" t="n">
-        <v>70.55</v>
+        <v>64.08</v>
       </c>
       <c r="G39" t="n">
-        <v>10.22</v>
+        <v>3.4</v>
       </c>
       <c r="H39" t="n">
         <v>5</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>170.31</v>
+        <v>424.1</v>
       </c>
       <c r="D40" t="n">
-        <v>182.69</v>
+        <v>474.82</v>
       </c>
       <c r="E40" t="n">
-        <v>-6.8</v>
+        <v>-10.7</v>
       </c>
       <c r="F40" t="n">
-        <v>69.05</v>
+        <v>70.55</v>
       </c>
       <c r="G40" t="n">
-        <v>0.74</v>
+        <v>10.22</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>55.03</v>
+        <v>170.31</v>
       </c>
       <c r="D41" t="n">
-        <v>53.54</v>
+        <v>182.69</v>
       </c>
       <c r="E41" t="n">
-        <v>2.8</v>
+        <v>-6.8</v>
       </c>
       <c r="F41" t="n">
-        <v>67.23</v>
+        <v>69.05</v>
       </c>
       <c r="G41" t="n">
-        <v>2.07</v>
+        <v>0.74</v>
       </c>
       <c r="H41" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>07-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>55.21</v>
+        <v>55.03</v>
       </c>
       <c r="D42" t="n">
-        <v>60.15</v>
+        <v>53.54</v>
       </c>
       <c r="E42" t="n">
-        <v>-8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="F42" t="n">
-        <v>73.01000000000001</v>
+        <v>67.23</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9</v>
+        <v>2.07</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>07-09-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>262.05</v>
+        <v>55.21</v>
       </c>
       <c r="D43" t="n">
-        <v>269.7</v>
+        <v>60.15</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F43" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="H43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>85.8</v>
+        <v>262.05</v>
       </c>
       <c r="D44" t="n">
-        <v>95.54000000000001</v>
+        <v>269.7</v>
       </c>
       <c r="E44" t="n">
-        <v>-10.2</v>
+        <v>-2.8</v>
       </c>
       <c r="F44" t="n">
-        <v>71.72</v>
+        <v>73.09</v>
       </c>
       <c r="G44" t="n">
-        <v>10.87</v>
+        <v>1.48</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -11046,173 +11228,208 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>65.72</v>
+        <v>85.8</v>
       </c>
       <c r="D45" t="n">
-        <v>64.04000000000001</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>2.6</v>
+        <v>-10.2</v>
       </c>
       <c r="F45" t="n">
-        <v>64.29000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="G45" t="n">
-        <v>0.31</v>
+        <v>10.87</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>268.05</v>
+        <v>65.72</v>
       </c>
       <c r="D46" t="n">
-        <v>292.28</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>-8.300000000000001</v>
+        <v>2.6</v>
       </c>
       <c r="F46" t="n">
-        <v>70.45</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>1.29</v>
+        <v>0.31</v>
       </c>
       <c r="H46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>171.96</v>
+        <v>268.05</v>
       </c>
       <c r="D47" t="n">
-        <v>174.99</v>
+        <v>292.28</v>
       </c>
       <c r="E47" t="n">
-        <v>-1.7</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="G47" t="n">
-        <v>0.79</v>
+        <v>1.29</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>28.08</v>
+        <v>171.96</v>
       </c>
       <c r="D48" t="n">
-        <v>34.64</v>
+        <v>174.99</v>
       </c>
       <c r="E48" t="n">
-        <v>-18.9</v>
+        <v>-1.7</v>
       </c>
       <c r="F48" t="n">
-        <v>61.81</v>
+        <v>65.64</v>
       </c>
       <c r="G48" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.79</v>
       </c>
       <c r="H48" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>WCIL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>82.78</v>
+        <v>28.08</v>
       </c>
       <c r="D49" t="n">
-        <v>102.08</v>
+        <v>34.64</v>
       </c>
       <c r="E49" t="n">
         <v>-18.9</v>
       </c>
       <c r="F49" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="H49" t="n">
+        <v>11</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>24-08-2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>WCIL</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>82.78</v>
+      </c>
+      <c r="D50" t="n">
+        <v>102.08</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-18.9</v>
+      </c>
+      <c r="F50" t="n">
         <v>71.89</v>
       </c>
-      <c r="G49" t="n">
+      <c r="G50" t="n">
         <v>0.47</v>
       </c>
-      <c r="H49" t="n">
+      <c r="H50" t="n">
         <v>4</v>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>30-06-2026</t>
         </is>
@@ -11251,7 +11468,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -11291,7 +11508,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -11311,7 +11528,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -11331,7 +11548,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
@@ -11341,7 +11558,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
